--- a/backend/data/financials_by_company/002026.SZ.xlsx
+++ b/backend/data/financials_by_company/002026.SZ.xlsx
@@ -4084,187 +4084,187 @@
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EY1" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Shandong Weida Machinery Co., Ltd. engages in the manufacture and sale of drill chucks in China and internationally. The company offers various types of drill chucks, including keyless chuck, keyless chuck with lock, key-type drill chuck, keyless automatic duty drill, and accessories, as well as saw blades. It also provides precision castings, such as power tools accessories, machining products, auto parts, hardware and tools, instrument valves, and die-casting and other casting products. In addition, the company offers powder metallurgy parts comprising structure parts, oiliness bearings, chain wheels, pulleys for engines, helix gears and impacted blocks for impacted power, and over loading parts for impacted power drills; and parts for oil pump of automobiles and angular connected axels, angular grinders,combination saw, narrow gutter saw blade, keyhole saw blade, wide gutter saw blade, laser welding saw blade, metallurgical saw blade, non-ferrous metal cutting, woodworking saw, metal cold cutting saw, double and single speed and impacted gear boxes, electric screwdrivers, and single and double speed gear boxes. Further, the company provides AC and DC switches, and CNC machines. It offers its products primarily under the Peacock, Jiyiji, DEMAC, and Weida brand names. Shandong Weida Machinery Co., Ltd. was founded in 1976 and is based in Wendeng, China.</t>
+          <t>Shandong Weida Machinery Co., Ltd. engages in the manufacture and sale of drill chucks in China and internationally. The company operates through three segments: power tool accessories, new energy, and high-end intelligent equipment manufacturing. It engages in the research, development, production, and sales of various specifications and models of drill chucks and accessories, power tool switches, new energy storage, lithium batteries, powder metallurgy parts, precision castings, saw blades, and machine tools. It also provides solutions for factory automation, logistics, automation, robotics and intelligent equipment, and fast battery swapping stations for new energy vehicles. In addition, it and leases non-residential and residential real estate. The company serves power tools, automobiles, electronics, fine chemicals, food and beverage, high-end equipment, and military industries. It offers its products primarily under the Peacock, Kongque, Jiyiji, DEMAC, and WEIDA brand names. Shandong Weida Machinery Co., Ltd. was founded in 1976 and is based in Wendeng, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4369,34 +4369,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>11.99</v>
+        <v>11.08</v>
       </c>
       <c r="V2" t="n">
-        <v>11.95</v>
+        <v>11.33</v>
       </c>
       <c r="W2" t="n">
-        <v>11.22</v>
+        <v>11.12</v>
       </c>
       <c r="X2" t="n">
-        <v>12.01</v>
+        <v>11.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.99</v>
+        <v>11.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.95</v>
+        <v>11.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.22</v>
+        <v>11.12</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.01</v>
+        <v>11.64</v>
       </c>
       <c r="AC2" t="n">
         <v>0.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
         <v>1764806400</v>
@@ -4405,37 +4405,37 @@
         <v>0.2203</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.54</v>
+        <v>0.555</v>
       </c>
       <c r="AI2" t="n">
-        <v>19.864408</v>
+        <v>19.152544</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.378641</v>
+        <v>10.970874</v>
       </c>
       <c r="AK2" t="n">
-        <v>9891700</v>
+        <v>9491212</v>
       </c>
       <c r="AL2" t="n">
-        <v>9891700</v>
+        <v>9491212</v>
       </c>
       <c r="AM2" t="n">
-        <v>6785427</v>
+        <v>7003295</v>
       </c>
       <c r="AN2" t="n">
-        <v>5876610</v>
+        <v>7007916</v>
       </c>
       <c r="AO2" t="n">
-        <v>5876610</v>
+        <v>7007916</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.71</v>
+        <v>11.32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.72</v>
+        <v>11.33</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4444,13 +4444,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>5163034624</v>
+        <v>4978011136</v>
       </c>
       <c r="AU2" t="n">
-        <v>5281977948</v>
+        <v>4770960899</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.22</v>
+        <v>10.44</v>
       </c>
       <c r="AW2" t="n">
         <v>17.29</v>
@@ -4462,19 +4462,19 @@
         <v>1.814595</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.659588</v>
+        <v>2.5642786</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.7644</v>
+        <v>12.3926</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.19435</v>
+        <v>14.07485</v>
       </c>
       <c r="BC2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0058381986</v>
+        <v>0.0063176895</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3440147968</v>
+        <v>3255124736</v>
       </c>
       <c r="BH2" t="n">
         <v>0.13239999</v>
@@ -4497,10 +4497,10 @@
         <v>440531939</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43199003</v>
+        <v>0.42355</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.01632</v>
+        <v>0.010319999</v>
       </c>
       <c r="BM2" t="n">
         <v>440531939</v>
@@ -4509,7 +4509,7 @@
         <v>8.77</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.3363739</v>
+        <v>1.2884834</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4541,16 +4541,16 @@
         <v>1368403200</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.772</v>
+        <v>1.677</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13.807</v>
+        <v>13.064</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.008410453999999999</v>
+        <v>-0.056218088</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CC2" t="n">
         <v>0.05</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>11.72</v>
+        <v>11.3</v>
       </c>
       <c r="CG2" t="n">
         <v>13</v>
@@ -4683,138 +4683,138 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1783062243</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>finmb_11369799</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1.9855621</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
           <t>SHANDONG WEIDA MACHINERY CO</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>-2.2518725</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>finmb_11369799</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DX2" t="b">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Shandong Weida Machinery Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.22000027</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>11.12 - 11.64</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>7003295</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.8600006</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.08237554</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>10.44 - 17.29</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>-5.9900007</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.34644306</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-5.621809</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1618916340</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1618916340</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-1.0925999</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.08816551</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-2.77485</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.19714952</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EV2" t="b">
         <v>0</v>
       </c>
-      <c r="DY2" t="b">
+      <c r="EW2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>6785427</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.04456328</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>11.22 - 17.29</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>-5.5700006</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.32215154</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.8410454000000001</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1618916340</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1618916340</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-1.0443993</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.08182126000000001</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-2.47435</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.17431936</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>1782111855</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="n">
+      <c r="EX2" t="n">
         <v>1090891800000</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-0.2699995</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>11.22 - 12.01</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>Shandong Weida Machinery Co., Ltd.</t>
-        </is>
       </c>
       <c r="EY2" t="inlineStr"/>
     </row>
